--- a/ArquivoExcel/Cotações.xlsx
+++ b/ArquivoExcel/Cotações.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8576</v>
+        <v>5.3494</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>45759.91172538194</v>
+        <v>45964.72993153934</v>
       </c>
     </row>
     <row r="3">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.65779</v>
+        <v>6.15764</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45759.91172538194</v>
+        <v>45964.72993153934</v>
       </c>
     </row>
     <row r="4">
@@ -482,49 +482,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>502853000</v>
+        <v>575826</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45759.91172538194</v>
+        <v>45964.72993153934</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dólar</t>
+          <t>Libra</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8546</v>
+        <v>7.02505</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45761.82636843352</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Euro</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>6.64011</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>45761.82636843352</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Bitcoin</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>497501000</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>45761.82636843352</v>
+        <v>45964.72993153934</v>
       </c>
     </row>
   </sheetData>
